--- a/output/graficos_dimensiones/comunal_e_mat_a_2018_la araucania.xlsx
+++ b/output/graficos_dimensiones/comunal_e_mat_a_2018_la araucania.xlsx
@@ -141,7 +141,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 21:37</t>
+    <t xml:space="preserve">2026-09-10 00:45</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_e_mat_a_2018_la araucania.xlsx
+++ b/output/graficos_dimensiones/comunal_e_mat_a_2018_la araucania.xlsx
@@ -141,7 +141,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-10 00:45</t>
+    <t xml:space="preserve">2026-09-18 10:55</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_e_mat_a_2018_la araucania.xlsx
+++ b/output/graficos_dimensiones/comunal_e_mat_a_2018_la araucania.xlsx
@@ -141,7 +141,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 10:55</t>
+    <t xml:space="preserve">2026-09-23 14:14</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_e_mat_a_2018_la araucania.xlsx
+++ b/output/graficos_dimensiones/comunal_e_mat_a_2018_la araucania.xlsx
@@ -141,7 +141,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-23 14:14</t>
+    <t xml:space="preserve">2026-10-02 15:02</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_e_mat_a_2018_la araucania.xlsx
+++ b/output/graficos_dimensiones/comunal_e_mat_a_2018_la araucania.xlsx
@@ -141,7 +141,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 15:02</t>
+    <t xml:space="preserve">2026-10-05 14:00</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
